--- a/14家金控主要比率final 3.xlsx
+++ b/14家金控主要比率final 3.xlsx
@@ -1,34 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://enctc-my.sharepoint.com/personal/pao0918_ntpc_edu_tw/Documents/Analysis/DASHBOARD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{F7F7F3C4-6422-4DE0-97C5-84E3BCB2BFBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{515BB8F9-C090-4221-BAD8-83AAC0151F2C}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{F7F7F3C4-6422-4DE0-97C5-84E3BCB2BFBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5AEF8876-7FC7-4F31-BC6B-0C1CC4741AEC}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2970" yWindow="3495" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="14家金控主要比率" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -57,18 +44,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>消金貸款市占率(國內)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>信用卡流通卡數市占率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>信用卡消費金額市占率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>信託商品市占率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -89,10 +68,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>衍生性金融商品餘額市占率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>進出口信用狀市占率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -105,102 +80,110 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>中信金</t>
-  </si>
-  <si>
-    <t>玉山金</t>
-  </si>
-  <si>
-    <t>永豐金</t>
-  </si>
-  <si>
-    <t>富邦金</t>
-  </si>
-  <si>
-    <t>國泰金</t>
-  </si>
-  <si>
-    <t>華南金</t>
-  </si>
-  <si>
-    <t>第一金</t>
-  </si>
-  <si>
-    <t>元大金</t>
-  </si>
-  <si>
-    <t>兆豐金</t>
-  </si>
-  <si>
-    <t>合庫金</t>
-  </si>
-  <si>
-    <t>凱基金</t>
-  </si>
-  <si>
-    <t>國票金</t>
+    <t>市占率-證券(2025/06)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>市占率-票券(2025/06)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>市占率-產險(2025/06)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>市占率-投信(2025/06)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>臺股經紀市占率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>融資市占率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CP2保證市占率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CP2承銷市占率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>票券買賣市占率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>債券買賣市占率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>股權承銷IPO送件數市占率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>股權承銷SPO 送件數</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>複委託市占率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消金控貸款市占率(國內)</t>
+  </si>
+  <si>
+    <t>信用卡消費金控額市占率</t>
+  </si>
+  <si>
+    <t>衍生性金控融商品餘額市占率</t>
+  </si>
+  <si>
+    <t>公募基金控市占率</t>
+  </si>
+  <si>
+    <t>中信金控</t>
+  </si>
+  <si>
+    <t>玉山金控</t>
+  </si>
+  <si>
+    <t>永豐金控</t>
+  </si>
+  <si>
+    <t>富邦金控</t>
+  </si>
+  <si>
+    <t>國泰金控</t>
+  </si>
+  <si>
+    <t>華南金控</t>
+  </si>
+  <si>
+    <t>第一金控</t>
+  </si>
+  <si>
+    <t>元大金控</t>
+  </si>
+  <si>
+    <t>兆豐金控</t>
+  </si>
+  <si>
+    <t>台新新光金控</t>
+  </si>
+  <si>
+    <t>合庫金控</t>
+  </si>
+  <si>
+    <t>凱基金控</t>
+  </si>
+  <si>
+    <t>國票金控</t>
   </si>
   <si>
     <t>臺灣金控</t>
-  </si>
-  <si>
-    <t>市占率-證券(2025/06)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>市占率-票券(2025/06)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>市占率-產險(2025/06)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>市占率-投信(2025/06)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>臺股經紀市占率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>融資市占率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CP2保證市占率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CP2承銷市占率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>票券買賣市占率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>債券買賣市占率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>公募基金市占率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>台新新光金</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>股權承銷IPO送件數市占率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>股權承銷SPO 送件數</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>複委託市占率</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -212,7 +195,7 @@
     <numFmt numFmtId="176" formatCode="#,##0.######;\-#,##0.######"/>
     <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -772,36 +755,36 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Z19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" style="18" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.28515625" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.7109375" style="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.875" style="18" customWidth="1"/>
+    <col min="2" max="2" width="26.25" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.25" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.75" style="18" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="47" style="18" customWidth="1"/>
     <col min="6" max="6" width="42" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.75" style="6" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="42" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="37.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="37.28515625" style="6" customWidth="1"/>
-    <col min="12" max="12" width="50.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="37.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="37.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="29.7109375" style="6" customWidth="1"/>
-    <col min="17" max="17" width="27.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="37.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="37.25" style="6" customWidth="1"/>
+    <col min="12" max="12" width="50.125" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="37.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="37.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="29.75" style="6" customWidth="1"/>
+    <col min="17" max="17" width="27.375" style="6" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.75" style="6" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="50" style="6" customWidth="1"/>
-    <col min="20" max="20" width="39.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="28.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="29.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="28.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="29.75" style="6" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="38" style="6" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="40.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="6"/>
+    <col min="26" max="26" width="40.125" style="6" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" ht="34.5" customHeight="1">
       <c r="A1" s="33"/>
       <c r="B1" s="37" t="s">
         <v>0</v>
@@ -824,102 +807,102 @@
       <c r="N1" s="36"/>
       <c r="O1" s="36"/>
       <c r="P1" s="39" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="39"/>
       <c r="R1" s="39"/>
       <c r="S1" s="39"/>
       <c r="T1" s="39"/>
       <c r="U1" s="35" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="V1" s="35"/>
       <c r="W1" s="35"/>
       <c r="X1" s="35"/>
       <c r="Y1" s="23" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="Z1" s="24" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:26" ht="29.25" customHeight="1">
       <c r="A2" s="34"/>
       <c r="B2" s="38"/>
       <c r="C2" s="38"/>
       <c r="D2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="L2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>17</v>
-      </c>
       <c r="P2" s="25" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="Q2" s="25" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="R2" s="21" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="S2" s="25" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="T2" s="25" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="U2" s="22" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="V2" s="22" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="W2" s="22" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="X2" s="22" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="Y2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="Z2" s="24" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="36.75" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B3" s="8">
         <v>7.46</v>
@@ -997,9 +980,9 @@
         <v>5.69</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" ht="36.75" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B4" s="8">
         <v>6.68</v>
@@ -1077,9 +1060,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" ht="36.75" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B5" s="8">
         <v>6.18</v>
@@ -1157,9 +1140,9 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" ht="36.75" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B6" s="8">
         <v>5.7</v>
@@ -1237,9 +1220,9 @@
         <v>8.8800000000000008</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" ht="36.75" customHeight="1">
       <c r="A7" s="7" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B7" s="8">
         <v>5.44</v>
@@ -1317,9 +1300,9 @@
         <v>13.71</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" ht="36.75" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="B8" s="8">
         <v>5.37</v>
@@ -1397,9 +1380,9 @@
         <v>0.54</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" ht="36.75" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B9" s="8">
         <v>5.26</v>
@@ -1477,9 +1460,9 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" ht="36.75" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B10" s="8">
         <v>5.26</v>
@@ -1557,9 +1540,9 @@
         <v>24.68</v>
       </c>
     </row>
-    <row r="11" spans="1:26" s="15" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" s="15" customFormat="1" ht="36.75" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B11" s="12">
         <v>5.01</v>
@@ -1637,9 +1620,9 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" ht="36.75" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="8">
         <v>4.63</v>
@@ -1719,9 +1702,9 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" ht="36.75" customHeight="1">
       <c r="A13" s="7" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B13" s="8">
         <v>3.87</v>
@@ -1799,9 +1782,9 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" ht="36.75" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B14" s="8">
         <v>1.91</v>
@@ -1879,9 +1862,9 @@
         <v>2.86</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" ht="36.75" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B15" s="8">
         <v>1.4</v>
@@ -1959,9 +1942,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:26" ht="36.75" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B16" s="8">
         <v>0.73</v>
@@ -2039,10 +2022,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18" s="19"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" s="19"/>
       <c r="B19" s="20"/>
     </row>
@@ -2059,7 +2042,7 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" scale="41" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A15 B3:B8 A3 A4:A8 A16 B9:B16 A9:A11 A13:A14" numberStoredAsText="1"/>
+    <ignoredError sqref="B3:B8 B9:B16" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>